--- a/Datas/Functions.xlsx
+++ b/Datas/Functions.xlsx
@@ -18,11 +18,86 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+  <si>
+    <t>PCNC</t>
+  </si>
+  <si>
+    <t>PCC</t>
+  </si>
+  <si>
+    <t>Lecteur</t>
+  </si>
+  <si>
+    <t>Distributeur</t>
+  </si>
+  <si>
+    <t>SAD</t>
+  </si>
+  <si>
+    <t>SIB</t>
+  </si>
+  <si>
+    <t>S'authentifier</t>
+  </si>
+  <si>
+    <t>Autoriser Transaction</t>
+  </si>
+  <si>
+    <t>Consulter</t>
+  </si>
+  <si>
+    <t>Consulter Details</t>
+  </si>
+  <si>
+    <t>Editer RIB</t>
+  </si>
+  <si>
+    <t>Retirer Argent</t>
+  </si>
+  <si>
+    <t>Deposer Argent</t>
+  </si>
+  <si>
+    <t>Deposer Cheque</t>
+  </si>
+  <si>
+    <t>Recharger Distributeur</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>Maintenancier</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,8 +124,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -69,7 +152,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -114,7 +197,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +232,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -331,9 +414,177 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" customWidth="1"/>
+    <col min="3" max="4" width="13.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" spans="1:9" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Datas/Functions.xlsx
+++ b/Datas/Functions.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>PCNC</t>
   </si>
@@ -462,7 +462,9 @@
         <v>15</v>
       </c>
       <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -480,7 +482,9 @@
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="H3" s="4"/>
     </row>
     <row r="4" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -495,7 +499,9 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -537,7 +543,9 @@
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4" t="s">
+        <v>15</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
